--- a/registration_forms/036_crop_innovation_day_registration_form--registration_forms.xlsx
+++ b/registration_forms/036_crop_innovation_day_registration_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -726,7 +726,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Format: example@domain.com</t>
+          <t>Format - example@domain.com</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Format: 123-456-7890</t>
+          <t>Format - 123-456-7890</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -839,12 +839,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>output_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Output</t>
+          <t>Output 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1000,12 +1000,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_one_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Select One</t>
+          <t>Select One 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1023,12 +1023,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_multiple_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Select Multiple</t>
+          <t>Select Multiple 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>date_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Date 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>time_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Time 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>decimal_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>Decimal 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1118,7 +1118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1338,29 +1338,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_multiple_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Option 4</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1372,12 +1372,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1389,182 +1389,114 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_one_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_one_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Option 4</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_multiple_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_multiple_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_multiple_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Option 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>option_1</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Option 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Option 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>option_4</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Option 4</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
